--- a/data/trans_orig/P19E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2016</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2016 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83012</t>
+          <t>84288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94369</t>
+          <t>91984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127451</t>
+          <t>126041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154096</t>
+          <t>152715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201220</t>
+          <t>198721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78051</t>
+          <t>78369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111423</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96765</t>
+          <t>98835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131647</t>
+          <t>132271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185320</t>
+          <t>187433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231817</t>
+          <t>233339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102379</t>
+          <t>102418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36605</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114265</t>
+          <t>113056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155718</t>
+          <t>155729</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>38039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32624</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38521</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153162</t>
+          <t>154085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195335</t>
+          <t>193575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206531</t>
+          <t>207283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253299</t>
+          <t>255995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374097</t>
+          <t>374269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>439581</t>
+          <t>434761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>120391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161879</t>
+          <t>162137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>129787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173599</t>
+          <t>171855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262454</t>
+          <t>260740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320930</t>
+          <t>319605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97606</t>
+          <t>97144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134851</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69037</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>106070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173733</t>
+          <t>178796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226863</t>
+          <t>230426</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>37479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54169</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53191</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85410</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154553</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187747</t>
+          <t>187872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208913</t>
+          <t>207795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243102</t>
+          <t>242520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375303</t>
+          <t>374211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>425260</t>
+          <t>425754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>98409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130973</t>
+          <t>131707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66789</t>
+          <t>67107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98819</t>
+          <t>99069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>172135</t>
+          <t>173643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216861</t>
+          <t>219854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>35372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56478</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92081</t>
+          <t>91200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126947</t>
+          <t>128004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128281</t>
+          <t>128279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166509</t>
+          <t>168600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>229328</t>
+          <t>230627</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282079</t>
+          <t>282481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123919</t>
+          <t>124958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>120656</t>
+          <t>121566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>161359</t>
+          <t>160892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223971</t>
+          <t>220151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>274451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88178</t>
+          <t>86439</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123294</t>
+          <t>122304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>70802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103568</t>
+          <t>106472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>166582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>214531</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>32967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42395</t>
+          <t>41685</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67675</t>
+          <t>67845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>45879</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>71068</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93336</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129641</t>
+          <t>128760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61344</t>
+          <t>61047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>87665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>80356</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108539</t>
+          <t>110080</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>150362</t>
+          <t>150599</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190516</t>
+          <t>188615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85766</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65150</t>
+          <t>67616</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>107522</t>
+          <t>108013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>143190</t>
+          <t>142655</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>47804</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>47344</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52586</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>81283</t>
+          <t>80361</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>78410</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>109610</t>
+          <t>109278</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>139640</t>
+          <t>140637</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>182349</t>
+          <t>182625</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98932</t>
+          <t>98958</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69762</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>102108</t>
+          <t>99810</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>147855</t>
+          <t>145767</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>188345</t>
+          <t>190584</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>69033</t>
+          <t>68159</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>98664</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>73073</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120326</t>
+          <t>120457</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>161698</t>
+          <t>162949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>137573</t>
+          <t>139602</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>186908</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>208045</t>
+          <t>207616</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>257841</t>
+          <t>258762</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>361218</t>
+          <t>362082</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>428898</t>
+          <t>427354</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>138954</t>
+          <t>135926</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>182304</t>
+          <t>181475</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>178034</t>
+          <t>179767</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>226169</t>
+          <t>227303</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>328426</t>
+          <t>331894</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>396881</t>
+          <t>399417</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>197063</t>
+          <t>198447</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>248265</t>
+          <t>247146</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>141043</t>
+          <t>139645</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>187733</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>348584</t>
+          <t>349997</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>416984</t>
+          <t>421499</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>47690</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>82677</t>
+          <t>80348</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>63152</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>371476</t>
+          <t>370249</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>423368</t>
+          <t>426869</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>426735</t>
+          <t>428187</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>486443</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>816019</t>
+          <t>815486</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>900373</t>
+          <t>895197</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>210372</t>
+          <t>210949</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>260737</t>
+          <t>261295</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>225681</t>
+          <t>222850</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>282409</t>
+          <t>280172</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>446498</t>
+          <t>452539</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>522843</t>
+          <t>526062</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>82319</t>
+          <t>82943</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>119035</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>80062</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>116302</t>
+          <t>118532</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>172672</t>
+          <t>173449</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>225911</t>
+          <t>223244</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1103420</t>
+          <t>1100283</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1220728</t>
+          <t>1215794</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1442619</t>
+          <t>1440558</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1557325</t>
+          <t>1561363</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2579294</t>
+          <t>2571155</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2736284</t>
+          <t>2738379</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>933260</t>
+          <t>940335</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1041499</t>
+          <t>1044347</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1075837</t>
+          <t>1074833</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1188330</t>
+          <t>1187888</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2044205</t>
+          <t>2044869</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2197429</t>
+          <t>2189857</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>751812</t>
+          <t>756770</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>851831</t>
+          <t>857481</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>595021</t>
+          <t>598814</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>685391</t>
+          <t>688044</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1380698</t>
+          <t>1375725</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1510638</t>
+          <t>1514181</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>119243</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>47192</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>80113</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>137078</t>
+          <t>137526</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>188277</t>
+          <t>190446</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>215499</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>275557</t>
+          <t>274402</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>101276</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>147562</t>
+          <t>151579</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>331996</t>
+          <t>332526</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>405798</t>
+          <t>407114</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2023</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2023 (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>45831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>79382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173842</t>
+          <t>174253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212112</t>
+          <t>214216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171618</t>
+          <t>171807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197784</t>
+          <t>197945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353811</t>
+          <t>354855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402630</t>
+          <t>402557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>63421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98563</t>
+          <t>95330</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50937</t>
+          <t>50987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121543</t>
+          <t>122248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158286</t>
+          <t>158733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>32492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50976</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96409</t>
+          <t>96934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78617</t>
+          <t>78204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111885</t>
+          <t>111984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138562</t>
+          <t>139190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195721</t>
+          <t>192831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221492</t>
+          <t>219950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279406</t>
+          <t>281143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272297</t>
+          <t>272474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312632</t>
+          <t>312468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505521</t>
+          <t>506660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>574986</t>
+          <t>576710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142624</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195127</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92477</t>
+          <t>91582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122912</t>
+          <t>122087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>249454</t>
+          <t>246019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>306809</t>
+          <t>310794</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>25520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52201</t>
+          <t>52798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39235</t>
+          <t>39535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66138</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76801</t>
+          <t>77101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106383</t>
+          <t>105141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123675</t>
+          <t>123676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164660</t>
+          <t>164756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120749</t>
+          <t>120667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154391</t>
+          <t>154981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150609</t>
+          <t>151266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183033</t>
+          <t>183710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281661</t>
+          <t>279162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327730</t>
+          <t>326680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114397</t>
+          <t>116400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56499</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80961</t>
+          <t>80183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146875</t>
+          <t>145294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>187047</t>
+          <t>187034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>43974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>107511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153349</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129301</t>
+          <t>132207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270526</t>
+          <t>272605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258534</t>
+          <t>246318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408386</t>
+          <t>404218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115945</t>
+          <t>115005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159905</t>
+          <t>158631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148079</t>
+          <t>145743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314584</t>
+          <t>310055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281179</t>
+          <t>282486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>459759</t>
+          <t>474530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23290</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49808</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52712</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91814</t>
+          <t>91254</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61663</t>
+          <t>61168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84408</t>
+          <t>84267</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>76323</t>
+          <t>75476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96001</t>
+          <t>95592</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>144706</t>
+          <t>145028</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174477</t>
+          <t>174173</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90987</t>
+          <t>90991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113413</t>
+          <t>113995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>108598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128321</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204275</t>
+          <t>204279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>234577</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,47 +10074,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2386</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2386</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>5210</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63334</t>
+          <t>60672</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>111993</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>142353</t>
+          <t>141993</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>124036</t>
+          <t>124505</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>149945</t>
+          <t>148843</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>243772</t>
+          <t>242809</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>284410</t>
+          <t>280815</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>83666</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>110946</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>82886</t>
+          <t>81621</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>150303</t>
+          <t>151117</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>184362</t>
+          <t>185338</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>40887</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>163667</t>
+          <t>163153</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>219904</t>
+          <t>220298</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>109795</t>
+          <t>110508</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>354777</t>
+          <t>358043</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>282617</t>
+          <t>278527</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>542737</t>
+          <t>542067</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>239683</t>
+          <t>240398</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>297219</t>
+          <t>300241</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>393595</t>
+          <t>394209</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>703784</t>
+          <t>710032</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>646526</t>
+          <t>654456</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1021685</t>
+          <t>1041754</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>109865</t>
+          <t>108976</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>160088</t>
+          <t>161975</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>87122</t>
+          <t>86577</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>128898</t>
+          <t>116757</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>238964</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17736</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>199378</t>
+          <t>197235</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>689887</t>
+          <t>693997</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>257168</t>
+          <t>257020</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>304667</t>
+          <t>306433</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>500764</t>
+          <t>497195</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1048733</t>
+          <t>1042027</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>198457</t>
+          <t>191836</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>607232</t>
+          <t>607874</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>344926</t>
+          <t>342570</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>393516</t>
+          <t>393456</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>500604</t>
+          <t>494634</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>960961</t>
+          <t>962312</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>26418</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>93208</t>
+          <t>96346</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>53736</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>66920</t>
+          <t>67248</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>132134</t>
+          <t>136018</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>751747</t>
+          <t>751121</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1482760</t>
+          <t>1485227</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>899231</t>
+          <t>887641</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1197213</t>
+          <t>1188041</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1818475</t>
+          <t>1826196</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2687501</t>
+          <t>2633255</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -12669,17 +12669,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1654233</t>
+          <t>1654234</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1322834</t>
+          <t>1275541</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1803736</t>
+          <t>1798859</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1848675</t>
+          <t>1855371</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2301239</t>
+          <t>2298583</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>3268681</t>
+          <t>3276998</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3926664</t>
+          <t>3911781</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>534860</t>
+          <t>522817</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>753854</t>
+          <t>755701</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>372497</t>
+          <t>362353</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>493686</t>
+          <t>493292</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>965977</t>
+          <t>987266</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1221945</t>
+          <t>1221534</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>70028</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>93088</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,47 +13063,47 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>183146</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>153818</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>211572</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>183146</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>156317</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>212659</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84288</t>
+          <t>82298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91984</t>
+          <t>94285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126041</t>
+          <t>125839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152715</t>
+          <t>153617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198721</t>
+          <t>200074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78369</t>
+          <t>79308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112112</t>
+          <t>111412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98835</t>
+          <t>97431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132271</t>
+          <t>130918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187433</t>
+          <t>183686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233339</t>
+          <t>232635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71826</t>
+          <t>69847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102418</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>61665</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113056</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>154272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31910</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39905</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154085</t>
+          <t>152845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193575</t>
+          <t>195061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207283</t>
+          <t>209546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255995</t>
+          <t>254800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374269</t>
+          <t>371724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>434761</t>
+          <t>435737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120391</t>
+          <t>120821</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162137</t>
+          <t>161586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129787</t>
+          <t>130391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>173246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260740</t>
+          <t>263726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319605</t>
+          <t>322494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97144</t>
+          <t>98255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134541</t>
+          <t>135573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69358</t>
+          <t>69826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106070</t>
+          <t>103990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178796</t>
+          <t>175880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>230426</t>
+          <t>229776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37479</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54480</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40252</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>52595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86285</t>
+          <t>85684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153414</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187872</t>
+          <t>188117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>207795</t>
+          <t>209018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242520</t>
+          <t>244285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>374211</t>
+          <t>375581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>425754</t>
+          <t>424294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>97335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>130456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67107</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99069</t>
+          <t>98570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173643</t>
+          <t>170430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219854</t>
+          <t>215896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35372</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>56513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>90860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128004</t>
+          <t>127869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128279</t>
+          <t>126323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168600</t>
+          <t>166255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230627</t>
+          <t>229616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282481</t>
+          <t>281655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>87431</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124958</t>
+          <t>123251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121566</t>
+          <t>123222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>160892</t>
+          <t>162716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220151</t>
+          <t>221015</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274451</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>87414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122304</t>
+          <t>121820</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70802</t>
+          <t>71287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>106472</t>
+          <t>104682</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>166582</t>
+          <t>167261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>216340</t>
+          <t>216456</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,82 +3131,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>13717</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>7959</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>22872</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>13717</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>7520</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>23048</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59254</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41685</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67845</t>
+          <t>67264</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45879</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71068</t>
+          <t>69968</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>128760</t>
+          <t>131212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>88931</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>80649</t>
+          <t>81902</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>110243</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>150599</t>
+          <t>151887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188615</t>
+          <t>189887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59295</t>
+          <t>58723</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85321</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67616</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>108013</t>
+          <t>107029</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142655</t>
+          <t>143301</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>47804</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>47344</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>78031</t>
+          <t>79720</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80361</t>
+          <t>79459</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>78410</t>
+          <t>77481</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>109278</t>
+          <t>109231</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>140637</t>
+          <t>137977</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>181505</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69267</t>
+          <t>68291</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98958</t>
+          <t>98432</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>69916</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>99810</t>
+          <t>100024</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>145767</t>
+          <t>146272</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>190584</t>
+          <t>188440</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68380</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>98664</t>
+          <t>99045</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>73290</t>
+          <t>72278</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120457</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>162949</t>
+          <t>163800</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>139602</t>
+          <t>138820</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>186908</t>
+          <t>185246</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>207616</t>
+          <t>209796</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>258762</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>362082</t>
+          <t>360546</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>427354</t>
+          <t>428190</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>135926</t>
+          <t>139800</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>181475</t>
+          <t>183405</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>179767</t>
+          <t>178315</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>227303</t>
+          <t>226430</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>331894</t>
+          <t>330169</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>399417</t>
+          <t>397256</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>198447</t>
+          <t>198061</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>247146</t>
+          <t>247022</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>139645</t>
+          <t>141342</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>186973</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>349997</t>
+          <t>353728</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>421499</t>
+          <t>418800</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>50666</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>46477</t>
+          <t>46869</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>80348</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>48273</t>
+          <t>47642</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>35173</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>369512</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>426869</t>
+          <t>425476</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>428187</t>
+          <t>425998</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>486443</t>
+          <t>486523</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>815486</t>
+          <t>815309</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>895197</t>
+          <t>898403</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>210949</t>
+          <t>212453</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>261295</t>
+          <t>265244</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>222850</t>
+          <t>226054</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>280172</t>
+          <t>284253</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>452539</t>
+          <t>450226</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>526062</t>
+          <t>522858</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>82943</t>
+          <t>82308</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>119035</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>118532</t>
+          <t>119312</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>173449</t>
+          <t>173268</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>223974</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>34473</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1100283</t>
+          <t>1110462</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1215794</t>
+          <t>1223826</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1440558</t>
+          <t>1446213</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1561363</t>
+          <t>1564130</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2571155</t>
+          <t>2572904</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2738379</t>
+          <t>2737292</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>940335</t>
+          <t>937875</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1044347</t>
+          <t>1038558</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1074833</t>
+          <t>1074389</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1187888</t>
+          <t>1185600</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2044869</t>
+          <t>2057948</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2189857</t>
+          <t>2211712</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>754717</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>857481</t>
+          <t>855965</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>598814</t>
+          <t>594866</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>688044</t>
+          <t>684666</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1375725</t>
+          <t>1376762</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1514181</t>
+          <t>1517562</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>120620</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>48552</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>81015</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>137526</t>
+          <t>134713</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>190446</t>
+          <t>189243</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>212137</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>274402</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>100645</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>151579</t>
+          <t>146944</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>332526</t>
+          <t>329157</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>407114</t>
+          <t>402284</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -7100,32 +7100,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26152</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32916</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43623</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7170,32 +7170,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>43241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79382</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -7213,32 +7213,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>193844</t>
+          <t>181520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174253</t>
+          <t>163023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214216</t>
+          <t>198785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7248,32 +7248,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>184526</t>
+          <t>199692</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171807</t>
+          <t>184689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>213606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7283,32 +7283,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>378370</t>
+          <t>381213</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354855</t>
+          <t>355496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402557</t>
+          <t>403176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -7326,32 +7326,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>99426</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>82428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95330</t>
+          <t>115474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7361,32 +7361,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>62344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71457</t>
+          <t>85756</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7396,32 +7396,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>173075</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122248</t>
+          <t>153460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158733</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -7474,32 +7474,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7509,32 +7509,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -7552,32 +7552,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7622,32 +7622,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7665,17 +7665,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311274</t>
+          <t>317956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311274</t>
+          <t>317956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311274</t>
+          <t>317956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7700,17 +7700,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>288881</t>
+          <t>315366</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>288881</t>
+          <t>315366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>288881</t>
+          <t>315366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7735,17 +7735,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>600156</t>
+          <t>633322</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>600156</t>
+          <t>633322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>600156</t>
+          <t>633322</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>75714</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>55849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96934</t>
+          <t>99543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93644</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78204</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111984</t>
+          <t>111683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>164510</t>
+          <t>170647</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139190</t>
+          <t>143618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192831</t>
+          <t>197826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>249704</t>
+          <t>252168</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219950</t>
+          <t>222347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281143</t>
+          <t>282439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>313734</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>293088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312468</t>
+          <t>336351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>543106</t>
+          <t>565902</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>506660</t>
+          <t>531204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576710</t>
+          <t>602533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -8008,32 +8008,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>169772</t>
+          <t>174328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144338</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196635</t>
+          <t>201560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106718</t>
+          <t>115140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>133029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>276490</t>
+          <t>289468</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>246019</t>
+          <t>260299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310794</t>
+          <t>320638</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8156,17 +8156,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8191,22 +8191,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8234,32 +8234,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8269,32 +8269,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8304,32 +8304,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39170</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28935</t>
+          <t>29124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -8347,17 +8347,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8382,17 +8382,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513651</t>
+          <t>544532</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513651</t>
+          <t>544532</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513651</t>
+          <t>544532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8417,17 +8417,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1032041</t>
+          <t>1075179</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1032041</t>
+          <t>1075179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1032041</t>
+          <t>1075179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66233</t>
+          <t>65721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>90598</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77101</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105141</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>142733</t>
+          <t>140654</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>121527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164756</t>
+          <t>163576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>138358</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120667</t>
+          <t>122098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154981</t>
+          <t>155806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>166810</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151266</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183710</t>
+          <t>187223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>304320</t>
+          <t>309067</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279162</t>
+          <t>284560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326680</t>
+          <t>329950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -8690,17 +8690,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99258</t>
+          <t>99288</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83659</t>
+          <t>83736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116400</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56252</t>
+          <t>59369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80183</t>
+          <t>83045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>166587</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145294</t>
+          <t>149866</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>187034</t>
+          <t>191188</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -8803,22 +8803,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8838,32 +8838,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8873,22 +8873,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19882</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8916,32 +8916,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8951,32 +8951,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8986,17 +8986,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9029,17 +9029,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>312542</t>
+          <t>312660</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>312542</t>
+          <t>312660</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>312542</t>
+          <t>312660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9064,17 +9064,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>346711</t>
+          <t>353937</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>346711</t>
+          <t>353937</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>346711</t>
+          <t>353937</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9099,17 +9099,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>659253</t>
+          <t>666598</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>659253</t>
+          <t>666598</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>659253</t>
+          <t>666598</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9146,32 +9146,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>129522</t>
+          <t>146323</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107511</t>
+          <t>120593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155208</t>
+          <t>170829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>220120</t>
+          <t>211826</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132207</t>
+          <t>188896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272605</t>
+          <t>230501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>349642</t>
+          <t>358149</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246318</t>
+          <t>325146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404218</t>
+          <t>391455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>136533</t>
+          <t>171796</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115005</t>
+          <t>146414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158631</t>
+          <t>198422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>202465</t>
+          <t>151511</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145743</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310055</t>
+          <t>170563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>338998</t>
+          <t>323307</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282486</t>
+          <t>292701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>474530</t>
+          <t>356072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -9372,32 +9372,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>71662</t>
+          <t>80322</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49375</t>
+          <t>64202</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>102999</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -9485,32 +9485,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>835</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -9598,32 +9598,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9668,32 +9668,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9711,17 +9711,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>307045</t>
+          <t>365539</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>307045</t>
+          <t>365539</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>307045</t>
+          <t>365539</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9746,17 +9746,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>465173</t>
+          <t>410560</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>465173</t>
+          <t>410560</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>465173</t>
+          <t>410560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>772218</t>
+          <t>776099</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>772218</t>
+          <t>776099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>772218</t>
+          <t>776099</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9828,32 +9828,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>72310</t>
+          <t>82880</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61168</t>
+          <t>69886</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>95432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>86086</t>
+          <t>93352</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>82425</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95592</t>
+          <t>104221</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>158396</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>145028</t>
+          <t>160086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174173</t>
+          <t>193650</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -9941,32 +9941,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>102747</t>
+          <t>118800</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90991</t>
+          <t>106669</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>132165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9976,32 +9976,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>117957</t>
+          <t>129034</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108598</t>
+          <t>117408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128747</t>
+          <t>139675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>220704</t>
+          <t>247834</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204279</t>
+          <t>230867</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>263575</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -10054,32 +10054,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>474</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10202,32 +10202,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10237,32 +10237,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>483</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>869</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10393,17 +10393,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207849</t>
+          <t>226384</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207849</t>
+          <t>226384</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207849</t>
+          <t>226384</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10463,17 +10463,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>386591</t>
+          <t>432049</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>386591</t>
+          <t>432049</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>386591</t>
+          <t>432049</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10510,32 +10510,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>61278</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -10623,32 +10623,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>123320</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>109044</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>141993</t>
+          <t>138022</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10658,32 +10658,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>136799</t>
+          <t>138879</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>124505</t>
+          <t>127171</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>148843</t>
+          <t>153797</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10693,32 +10693,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>263127</t>
+          <t>262199</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>242809</t>
+          <t>241375</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>280815</t>
+          <t>283095</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -10736,32 +10736,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>101035</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>83666</t>
+          <t>88035</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>110923</t>
+          <t>114582</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10771,32 +10771,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>73850</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60411</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>81621</t>
+          <t>84780</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10806,32 +10806,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>167362</t>
+          <t>174885</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>151117</t>
+          <t>157360</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>185338</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -10849,32 +10849,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10884,32 +10884,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10919,32 +10919,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -10962,32 +10962,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10997,32 +10997,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11032,32 +11032,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40887</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -11075,17 +11075,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>268897</t>
+          <t>269981</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>268897</t>
+          <t>269981</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>268897</t>
+          <t>269981</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11145,17 +11145,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>525953</t>
+          <t>533731</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>525953</t>
+          <t>533731</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>525953</t>
+          <t>533731</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11192,32 +11192,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>191475</t>
+          <t>231060</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>163153</t>
+          <t>200338</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>220298</t>
+          <t>263362</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11227,32 +11227,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>261330</t>
+          <t>309759</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>110508</t>
+          <t>286101</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>358043</t>
+          <t>336520</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11262,32 +11262,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>452805</t>
+          <t>540820</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>278527</t>
+          <t>500811</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>542067</t>
+          <t>578992</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -11305,32 +11305,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>268315</t>
+          <t>314085</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>240398</t>
+          <t>284012</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>300241</t>
+          <t>345158</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11340,32 +11340,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>510352</t>
+          <t>373827</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>394209</t>
+          <t>347059</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>710032</t>
+          <t>399163</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11375,32 +11375,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>778667</t>
+          <t>687913</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>654456</t>
+          <t>646804</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1041754</t>
+          <t>728315</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -11418,32 +11418,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>132385</t>
+          <t>138406</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>108976</t>
+          <t>115285</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>161975</t>
+          <t>163354</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>61412</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>86577</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11488,32 +11488,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>193797</t>
+          <t>207641</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>116757</t>
+          <t>179807</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>238964</t>
+          <t>236696</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -11531,32 +11531,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11601,32 +11601,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -11644,32 +11644,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11679,32 +11679,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11714,32 +11714,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>620448</t>
+          <t>715258</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>620448</t>
+          <t>715258</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>620448</t>
+          <t>715258</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11792,17 +11792,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>846100</t>
+          <t>767509</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>846100</t>
+          <t>767509</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>846100</t>
+          <t>767509</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11827,17 +11827,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1466548</t>
+          <t>1482768</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1466548</t>
+          <t>1482768</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1466548</t>
+          <t>1482768</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>398196</t>
+          <t>187393</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>197235</t>
+          <t>162085</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>693997</t>
+          <t>215150</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>281084</t>
+          <t>319016</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>257020</t>
+          <t>295143</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>306433</t>
+          <t>347339</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11944,32 +11944,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>679281</t>
+          <t>506409</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>497195</t>
+          <t>472878</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1042027</t>
+          <t>544091</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -11987,32 +11987,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>439252</t>
+          <t>507786</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>191836</t>
+          <t>478823</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>607874</t>
+          <t>536672</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12022,32 +12022,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>368711</t>
+          <t>434107</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>342570</t>
+          <t>406402</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>393456</t>
+          <t>460085</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12057,32 +12057,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>807963</t>
+          <t>941893</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>494634</t>
+          <t>903637</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>962312</t>
+          <t>980134</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -12100,32 +12100,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>64570</t>
+          <t>73313</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>58160</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>96346</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12135,32 +12135,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>53736</t>
+          <t>64591</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12170,32 +12170,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>107334</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>106203</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>136018</t>
+          <t>147535</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -12213,32 +12213,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12248,32 +12248,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12283,32 +12283,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>41477</t>
+          <t>44467</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -12326,32 +12326,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12361,27 +12361,27 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -12396,32 +12396,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -12439,17 +12439,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928116</t>
+          <t>797419</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928116</t>
+          <t>797419</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928116</t>
+          <t>797419</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12474,17 +12474,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1643508</t>
+          <t>1628028</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1643508</t>
+          <t>1628028</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1643508</t>
+          <t>1628028</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12556,32 +12556,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>959861</t>
+          <t>817272</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>751121</t>
+          <t>759590</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1485227</t>
+          <t>877719</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12591,32 +12591,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1094478</t>
+          <t>1178847</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>887641</t>
+          <t>1132618</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1188041</t>
+          <t>1231677</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12626,32 +12626,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2054339</t>
+          <t>1996119</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1826196</t>
+          <t>1921674</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2633255</t>
+          <t>2074178</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -12669,32 +12669,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1654234</t>
+          <t>1807833</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1275541</t>
+          <t>1744460</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1798859</t>
+          <t>1876095</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12704,32 +12704,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1981020</t>
+          <t>1911494</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1855371</t>
+          <t>1858606</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2298583</t>
+          <t>1964311</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12739,32 +12739,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>3635254</t>
+          <t>3719327</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>3276998</t>
+          <t>3627151</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3911781</t>
+          <t>3799616</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -12782,32 +12782,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>678711</t>
+          <t>727182</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>522817</t>
+          <t>680580</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>755701</t>
+          <t>783093</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12817,32 +12817,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>449028</t>
+          <t>498256</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>362353</t>
+          <t>464805</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>493292</t>
+          <t>537252</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12852,32 +12852,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>1127740</t>
+          <t>1225438</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>987266</t>
+          <t>1166955</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1221534</t>
+          <t>1289285</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -12895,32 +12895,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12930,32 +12930,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12965,32 +12965,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>95628</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>78318</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -13008,32 +13008,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>126818</t>
+          <t>132598</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13043,32 +13043,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>93088</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13078,32 +13078,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>183146</t>
+          <t>191261</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>153818</t>
+          <t>167070</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>217230</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -13121,17 +13121,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13156,17 +13156,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13191,17 +13191,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
